--- a/tame_output/MOZAIC/data/universe_last2023-07-28.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-28.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.2685070432987</v>
+        <v>567.8739753373341</v>
       </c>
       <c r="E2" t="n">
-        <v>10781.4372903021</v>
+        <v>11139.42069948786</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6172512259471381</v>
+        <v>0.6151655727910497</v>
       </c>
       <c r="G2" t="n">
-        <v>0.498657689371703</v>
+        <v>0.4986615472465565</v>
       </c>
       <c r="H2" t="n">
-        <v>1.237825544663435</v>
+        <v>1.23363346580018</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.7376977714407</v>
+        <v>224.3753161311582</v>
       </c>
       <c r="E3" t="n">
-        <v>4251.396734517274</v>
+        <v>3951.540015399553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2568276284942486</v>
+        <v>0.2610350377983077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5978024177536629</v>
+        <v>0.5978064438716441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4296195881229771</v>
+        <v>0.4366547742572593</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907351026948769</v>
+        <v>0.8907023590049311</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067833925593269</v>
+        <v>1.067793602143441</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.61595934806003</v>
+        <v>37.47942013696762</v>
       </c>
       <c r="E4" t="n">
-        <v>1473.550581363958</v>
+        <v>1474.299149368159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7929611286509537</v>
+        <v>0.7790724707817898</v>
       </c>
       <c r="G4" t="n">
-        <v>1.108526055696963</v>
+        <v>1.108557800244165</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7153292649962978</v>
+        <v>0.7027801983894713</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736164080096211</v>
+        <v>0.4736306981757394</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052858784441441</v>
+        <v>1.052912557218299</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.00860669044192</v>
+        <v>37.17462081046231</v>
       </c>
       <c r="E5" t="n">
-        <v>434.1708235204159</v>
+        <v>395.9866813278662</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.335575677099675</v>
+        <v>-0.3322150030053298</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5614146346465241</v>
+        <v>0.5614409938691729</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.597732328995946</v>
+        <v>-0.5917184648663946</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362692452609626</v>
+        <v>0.7361885689307968</v>
       </c>
       <c r="N5" t="n">
-        <v>0.828930021816107</v>
+        <v>0.8288716948356695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.88714741437063</v>
+        <v>10.90537551110779</v>
       </c>
       <c r="E6" t="n">
-        <v>502.8648197531176</v>
+        <v>158.3356696144105</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4856267998179666</v>
+        <v>-0.2995823886744731</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8141892272039739</v>
+        <v>0.7145067098958192</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5964544648738094</v>
+        <v>-0.4192856197503794</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J6" t="n">
         <v>270</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6679418397447033</v>
+        <v>0.7506830002703372</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09058992152343</v>
+        <v>1.075615402189175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.80974845088202</v>
+        <v>10.75971392941808</v>
       </c>
       <c r="E7" t="n">
-        <v>166.8007669199969</v>
+        <v>453.8989363602852</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3065623227358069</v>
+        <v>-0.494301819093537</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7143774570906122</v>
+        <v>0.81430652574447</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4291321341302099</v>
+        <v>-0.6070218074718576</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J7" t="n">
         <v>270</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7509000210424647</v>
+        <v>0.6679204449488391</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075740049727274</v>
+        <v>1.090703664646253</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.17767257667978</v>
+        <v>9.993134372591522</v>
       </c>
       <c r="E8" t="n">
-        <v>496.0889308851945</v>
+        <v>433.0770336772596</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.29201104429493</v>
+        <v>-0.3116730828690558</v>
       </c>
       <c r="G8" t="n">
-        <v>1.171492119036869</v>
+        <v>1.171647500069734</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2492641986657187</v>
+        <v>-0.2660126726259439</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375891418590601</v>
+        <v>0.7375714268021306</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732811676610816</v>
+        <v>1.732986477716727</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.423742606212331</v>
+        <v>7.493212135824386</v>
       </c>
       <c r="E9" t="n">
-        <v>204.7555881152148</v>
+        <v>200.9940095331705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4413307682911878</v>
+        <v>0.4580455885276853</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4797929918444439</v>
+        <v>0.479933413167844</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9198357954221096</v>
+        <v>0.9543940387569888</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,45 +922,45 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787154252881158</v>
+        <v>0.6784079755499109</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6530389713237185</v>
+        <v>0.6529291400625528</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.682130668734112</v>
+        <v>6.710492059898518</v>
       </c>
       <c r="E10" t="n">
-        <v>238.9785062573501</v>
+        <v>356.5230333939968</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2660520104752351</v>
+        <v>0.9835666158490519</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9583458543045392</v>
+        <v>0.8213950484780556</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.277615862040021</v>
+        <v>1.197434313332519</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J10" t="n">
         <v>270</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135129974095464</v>
+        <v>0.664256476317388</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371265775368683</v>
+        <v>1.094162931911031</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.665644839863776</v>
+        <v>6.630888337321552</v>
       </c>
       <c r="E11" t="n">
-        <v>389.2760114215592</v>
+        <v>235.4116909782205</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9724141652876743</v>
+        <v>-0.275019888855131</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8213755704557985</v>
+        <v>0.9583919239136238</v>
       </c>
       <c r="H11" t="n">
-        <v>1.183884936762925</v>
+        <v>-0.2869597311839592</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J11" t="n">
         <v>270</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643068929549912</v>
+        <v>0.7135211268236613</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094228495395559</v>
+        <v>1.371336709769268</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.322468046281659</v>
+        <v>6.315161222541204</v>
       </c>
       <c r="E12" t="n">
-        <v>97.2445431667734</v>
+        <v>95.92639189252645</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2726529339182815</v>
+        <v>-0.2735926204992624</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6583767153815945</v>
+        <v>0.6583800738839942</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4141290655460865</v>
+        <v>-0.4155542236952163</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889057430589035</v>
+        <v>0.7889082103845169</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041590620040825</v>
+        <v>1.0415911327204</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.763332007487707</v>
+        <v>4.738211387132897</v>
       </c>
       <c r="E13" t="n">
-        <v>222.6233124940634</v>
+        <v>163.8881391468475</v>
       </c>
       <c r="F13" t="n">
-        <v>1.779971886275533</v>
+        <v>1.755457363328228</v>
       </c>
       <c r="G13" t="n">
-        <v>0.860827304765964</v>
+        <v>0.860906641408984</v>
       </c>
       <c r="H13" t="n">
-        <v>2.067745616827825</v>
+        <v>2.039079824561693</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6036917337528486</v>
+        <v>0.6036853350958764</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042146424595866</v>
+        <v>1.042223362067822</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.552739671499623</v>
+        <v>4.533412205368158</v>
       </c>
       <c r="E14" t="n">
-        <v>91.73737578434908</v>
+        <v>86.02577456325091</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.402634983465067</v>
+        <v>-0.4075351194349192</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8502632474428269</v>
+        <v>0.8502736782644068</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4735415586596207</v>
+        <v>-0.4792987597437884</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760187841716602</v>
+        <v>0.7602048290316509</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296199370311345</v>
+        <v>1.296234208922292</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.345576512874832</v>
+        <v>4.345596280575641</v>
       </c>
       <c r="E15" t="n">
-        <v>305.2665979555644</v>
+        <v>301.8782681853694</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6264766645182751</v>
+        <v>0.6237202127049966</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9606939954196579</v>
+        <v>0.96069711005597</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6521084419233958</v>
+        <v>0.6492371072800029</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138343661256387</v>
+        <v>0.5138387554320851</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9899327749244955</v>
+        <v>0.9899367819798731</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.297760782746021</v>
+        <v>4.233923392522859</v>
       </c>
       <c r="E16" t="n">
-        <v>347.9967829405942</v>
+        <v>287.3613425224411</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02745403642254374</v>
+        <v>-0.0003440985897782411</v>
       </c>
       <c r="G16" t="n">
-        <v>0.793618975159695</v>
+        <v>0.7938772879070508</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03459347278965871</v>
+        <v>-0.0004334405266655381</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.714428287988198</v>
+        <v>0.7143174134894472</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137020159967203</v>
+        <v>1.137204931996484</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.391636488679292</v>
+        <v>3.430293483615437</v>
       </c>
       <c r="E17" t="n">
-        <v>73.69327443151349</v>
+        <v>67.05304856987267</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2034721547218561</v>
+        <v>-0.1911822890236649</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7532010740726287</v>
+        <v>0.7533404166678855</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.270143208402058</v>
+        <v>-0.2537794133882885</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7242461623534294</v>
+        <v>0.724022031323628</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093942796841063</v>
+        <v>1.093798111696765</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.091944069402133</v>
+        <v>3.101607850259819</v>
       </c>
       <c r="E18" t="n">
-        <v>54.56922731460989</v>
+        <v>52.71778786716115</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4710933808107163</v>
+        <v>-0.4703733707313172</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7457604666008159</v>
+        <v>0.7457682241949758</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6316952988376615</v>
+        <v>-0.6307232669225948</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645598949005089</v>
+        <v>0.764525845727737</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143426755704271</v>
+        <v>1.143378881864394</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.97103627821927</v>
+        <v>2.990294250998771</v>
       </c>
       <c r="E19" t="n">
-        <v>106.4722903022406</v>
+        <v>116.9999745612311</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1192370960618661</v>
+        <v>0.1257557389016679</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4812407860125562</v>
+        <v>0.4812960513660321</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2477701382084332</v>
+        <v>0.2612856235673311</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177419195933501</v>
+        <v>0.7175931957167673</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926729355652156</v>
+        <v>0.6926035775019297</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.670113835118673</v>
+        <v>2.627513319350845</v>
       </c>
       <c r="E20" t="n">
-        <v>101.8522193232513</v>
+        <v>116.9163532372442</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2957446232645845</v>
+        <v>-0.3079292666794879</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7785946185500326</v>
+        <v>0.7783470443367317</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3798441656523984</v>
+        <v>-0.3956194976520914</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322973699665067</v>
+        <v>0.7325560549733058</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143395165835417</v>
+        <v>1.143426525160821</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-28.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-28.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.8739753373341</v>
+        <v>569.8284542020242</v>
       </c>
       <c r="E2" t="n">
-        <v>11139.42069948786</v>
+        <v>11261.9129312367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6151655727910497</v>
+        <v>0.6217837661890484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4986615472465565</v>
+        <v>0.4986577059973233</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23363346580018</v>
+        <v>1.246914985391574</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.3753161311582</v>
+        <v>226.7087063041265</v>
       </c>
       <c r="E3" t="n">
-        <v>3951.540015399553</v>
+        <v>3866.851309417894</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2610350377983077</v>
+        <v>0.2692321638383275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5978064438716441</v>
+        <v>0.5978534877086563</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4366547742572593</v>
+        <v>0.4503313426675679</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907023590049311</v>
+        <v>0.8906881899650835</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067793602143441</v>
+        <v>1.067868869621747</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.47942013696762</v>
+        <v>37.51953647766354</v>
       </c>
       <c r="E4" t="n">
-        <v>1474.299149368159</v>
+        <v>1069.851127947799</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7790724707817898</v>
+        <v>0.782457355508092</v>
       </c>
       <c r="G4" t="n">
-        <v>1.108557800244165</v>
+        <v>1.108546399777586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7027801983894713</v>
+        <v>0.7058408702288697</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736306981757394</v>
+        <v>0.4735881858779094</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052912557218299</v>
+        <v>1.052815332277193</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.17462081046231</v>
+        <v>37.27786461149871</v>
       </c>
       <c r="E5" t="n">
-        <v>395.9866813278662</v>
+        <v>393.0739703399383</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3322150030053298</v>
+        <v>-0.329598097496309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5614409938691729</v>
+        <v>0.5614844670463559</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5917184648663946</v>
+        <v>-0.5870119599748385</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7361885689307968</v>
+        <v>0.7362214121889482</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8288716948356695</v>
+        <v>0.8289792422324379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.90537551110779</v>
+        <v>10.89258084419568</v>
       </c>
       <c r="E6" t="n">
-        <v>158.3356696144105</v>
+        <v>371.2766389281509</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2995823886744731</v>
+        <v>-0.4854475299292728</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7145067098958192</v>
+        <v>0.8141895001197936</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4192856197503794</v>
+        <v>-0.5962340829227688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J6" t="n">
         <v>270</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7506830002703372</v>
+        <v>0.6679460002971169</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075615402189175</v>
+        <v>1.090597043920633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.75971392941808</v>
+        <v>10.87218065951785</v>
       </c>
       <c r="E7" t="n">
-        <v>453.8989363602852</v>
+        <v>145.0241258733493</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.494301819093537</v>
+        <v>-0.3041365837731709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.81430652574447</v>
+        <v>0.7144105899974681</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6070218074718576</v>
+        <v>-0.4257167909202588</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J7" t="n">
         <v>270</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6679204449488391</v>
+        <v>0.7509181950511908</v>
       </c>
       <c r="N7" t="n">
-        <v>1.090703664646253</v>
+        <v>1.075815944112241</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.993134372591522</v>
+        <v>10.07480778577586</v>
       </c>
       <c r="E8" t="n">
-        <v>433.0770336772596</v>
+        <v>373.808549630849</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3116730828690558</v>
+        <v>-0.3037500016478387</v>
       </c>
       <c r="G8" t="n">
-        <v>1.171647500069734</v>
+        <v>1.171525952227067</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2660126726259439</v>
+        <v>-0.2592772281914976</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375714268021306</v>
+        <v>0.7375563395457549</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732986477716727</v>
+        <v>1.732784598764605</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.493212135824386</v>
+        <v>7.624397760804435</v>
       </c>
       <c r="E9" t="n">
-        <v>200.9940095331705</v>
+        <v>221.3835191157006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4580455885276853</v>
+        <v>0.4909135448187891</v>
       </c>
       <c r="G9" t="n">
-        <v>0.479933413167844</v>
+        <v>0.4808010737177297</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9543940387569888</v>
+        <v>1.021032546834528</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6784079755499109</v>
+        <v>0.677457604094011</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6529291400625528</v>
+        <v>0.6531982550940254</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.710492059898518</v>
+        <v>6.716318318952495</v>
       </c>
       <c r="E10" t="n">
-        <v>356.5230333939968</v>
+        <v>341.5200839403676</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9835666158490519</v>
+        <v>0.9844477691460909</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8213950484780556</v>
+        <v>0.8213978023948627</v>
       </c>
       <c r="H10" t="n">
-        <v>1.197434313332519</v>
+        <v>1.198503047215175</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.664256476317388</v>
+        <v>0.6643093646699849</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094162931911031</v>
+        <v>1.094262147536495</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.630888337321552</v>
+        <v>6.624943337740631</v>
       </c>
       <c r="E11" t="n">
-        <v>235.4116909782205</v>
+        <v>215.560759228545</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.275019888855131</v>
+        <v>-0.2780486603000687</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9583919239136238</v>
+        <v>0.9584334063877098</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2869597311839592</v>
+        <v>-0.2901074382914312</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135211268236613</v>
+        <v>0.7134176840395982</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371336709769268</v>
+        <v>1.371207810222776</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.315161222541204</v>
+        <v>6.305217139261146</v>
       </c>
       <c r="E12" t="n">
-        <v>95.92639189252645</v>
+        <v>98.80044164418054</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2735926204992624</v>
+        <v>-0.2764097817824683</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6583800738839942</v>
+        <v>0.6584012167041393</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4155542236952163</v>
+        <v>-0.419819670392068</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889082103845169</v>
+        <v>0.7888496224470252</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0415911327204</v>
+        <v>1.041555249160253</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.738211387132897</v>
+        <v>4.718208987928228</v>
       </c>
       <c r="E13" t="n">
-        <v>163.8881391468475</v>
+        <v>134.2148205222764</v>
       </c>
       <c r="F13" t="n">
-        <v>1.755457363328228</v>
+        <v>1.738636466784134</v>
       </c>
       <c r="G13" t="n">
-        <v>0.860906641408984</v>
+        <v>0.8609994310751344</v>
       </c>
       <c r="H13" t="n">
-        <v>2.039079824561693</v>
+        <v>2.019323595386224</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6036853350958764</v>
+        <v>0.6035059249736644</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042223362067822</v>
+        <v>1.042033947943416</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.533412205368158</v>
+        <v>4.582551325675755</v>
       </c>
       <c r="E14" t="n">
-        <v>86.02577456325091</v>
+        <v>80.18695820777097</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4075351194349192</v>
+        <v>-0.3983387626983826</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8502736782644068</v>
+        <v>0.8503017289930794</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4792987597437884</v>
+        <v>-0.4684675440682595</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602048290316509</v>
+        <v>0.760183525317236</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296234208922292</v>
+        <v>1.296250630753854</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.345596280575641</v>
+        <v>4.425816561488945</v>
       </c>
       <c r="E15" t="n">
-        <v>301.8782681853694</v>
+        <v>282.567947430477</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6237202127049966</v>
+        <v>0.6638074185104619</v>
       </c>
       <c r="G15" t="n">
-        <v>0.96069711005597</v>
+        <v>0.9608660506978187</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6492371072800029</v>
+        <v>0.6908428266649433</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138387554320851</v>
+        <v>0.513784693237119</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9899367819798731</v>
+        <v>0.9900143187647653</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.233923392522859</v>
+        <v>4.20965301802295</v>
       </c>
       <c r="E16" t="n">
-        <v>287.3613425224411</v>
+        <v>211.0778968940258</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0003440985897782411</v>
+        <v>-0.008421530610473238</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7938772879070508</v>
+        <v>0.7940812843719812</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0004334405266655381</v>
+        <v>-0.01060537601907293</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7143174134894472</v>
+        <v>0.7139382439359755</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137204931996484</v>
+        <v>1.136902109179477</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.430293483615437</v>
+        <v>3.467606213708891</v>
       </c>
       <c r="E17" t="n">
-        <v>67.05304856987267</v>
+        <v>67.84497001320466</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1911822890236649</v>
+        <v>-0.1803194519806036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7533404166678855</v>
+        <v>0.7536537103606765</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2537794133882885</v>
+        <v>-0.2392603519384361</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.724022031323628</v>
+        <v>0.7238991184941296</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093798111696765</v>
+        <v>1.094075655541664</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.101607850259819</v>
+        <v>3.128474239882283</v>
       </c>
       <c r="E18" t="n">
-        <v>52.71778786716115</v>
+        <v>52.33021033474334</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4703733707313172</v>
+        <v>-0.464604129253482</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7457682241949758</v>
+        <v>0.7458958847692232</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6307232669225948</v>
+        <v>-0.6228806710701031</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764525845727737</v>
+        <v>0.7644831293303653</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143378881864394</v>
+        <v>1.143519519070819</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.990294250998771</v>
+        <v>2.981010051891388</v>
       </c>
       <c r="E19" t="n">
-        <v>116.9999745612311</v>
+        <v>107.0615520223587</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1257557389016679</v>
+        <v>0.122029593587186</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4812960513660321</v>
+        <v>0.4812581457398117</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2612856235673311</v>
+        <v>0.2535636948016675</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7175931957167673</v>
+        <v>0.7177550436862453</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926035775019297</v>
+        <v>0.692710565314505</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.627513319350845</v>
+        <v>2.627701275780815</v>
       </c>
       <c r="E20" t="n">
-        <v>116.9163532372442</v>
+        <v>118.2294370415899</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3079292666794879</v>
+        <v>-0.3074226796706457</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7783470443367317</v>
+        <v>0.7783515365041459</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3956194976520914</v>
+        <v>-0.3949663683473801</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325560549733058</v>
+        <v>0.7326067552921447</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143426525160821</v>
+        <v>1.143521070218893</v>
       </c>
     </row>
   </sheetData>
